--- a/output/quickfixclose0_portfolio_daily.xlsx
+++ b/output/quickfixclose0_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$185</f>
+              <f>'equity_curve'!$A$2:$A$186</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$185</f>
+              <f>'equity_curve'!$B$2:$B$186</f>
             </numRef>
           </val>
         </ser>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-30</t>
+          <t>2025-12-18 -&gt; 2026-07-31</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H185"/>
+  <dimension ref="A1:H186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5201,6 +5201,26 @@
       <c r="F185" t="inlineStr"/>
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B186" s="5" t="n">
+        <v>504201.14</v>
+      </c>
+      <c r="C186" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D186" s="5" t="n">
+        <v>504201.14</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/quickfixclose0_portfolio_daily.xlsx
+++ b/output/quickfixclose0_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$186</f>
+              <f>'equity_curve'!$A$2:$A$188</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$186</f>
+              <f>'equity_curve'!$B$2:$B$188</f>
             </numRef>
           </val>
         </ser>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-31</t>
+          <t>2025-12-18 -&gt; 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5221,6 +5221,46 @@
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B187" s="5" t="n">
+        <v>504201.14</v>
+      </c>
+      <c r="C187" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D187" s="5" t="n">
+        <v>504201.14</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B188" s="5" t="n">
+        <v>504201.14</v>
+      </c>
+      <c r="C188" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D188" s="5" t="n">
+        <v>504201.14</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/quickfixclose0_portfolio_daily.xlsx
+++ b/output/quickfixclose0_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$188</f>
+              <f>'equity_curve'!$A$2:$A$190</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$188</f>
+              <f>'equity_curve'!$B$2:$B$190</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>504,201.14</t>
+          <t>524,424.45</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+404.20%</t>
+          <t>+424.42%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>520,101  (+420.10%)</t>
+          <t>541,057  (+441.06%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8,175  (15.9 pts of return)</t>
+          <t>8,266  (16.6 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7281.4x</t>
+          <t>7645.8x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>97.3%</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+1.63R  (best +9.14R)</t>
+          <t>+1.59R  (best +9.14R)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3,965  (+1.63%)</t>
+          <t>3,969  (+1.59%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-04</t>
+          <t>2025-12-18 -&gt; 2026-08-06</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5262,6 +5262,62 @@
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
     </row>
+    <row r="189">
+      <c r="A189" s="4" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B189" s="5" t="n">
+        <v>518246.71</v>
+      </c>
+      <c r="C189" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D189" s="5" t="n">
+        <v>518246.71</v>
+      </c>
+      <c r="E189" t="n">
+        <v>0</v>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures short (risk 5,042); Nasdaq_100_E_mini short (risk 4,992); S_P_500_E_mini short (risk 4,942)</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Nasdaq_100_E_mini exit_close (+7,652); NY_Platinum_Futures exit_close (+3,939); S_P_500_E_mini exit_close (+2,455)</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B190" s="5" t="n">
+        <v>524424.45</v>
+      </c>
+      <c r="C190" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>524424.45</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 5,182); NY_Platinum_Futures short (risk 5,131)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX exit_close (+487); NY_Platinum_Futures exit_close (+5,691)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5274,7 +5330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M106"/>
+  <dimension ref="A1:M111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10714,6 +10770,261 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.781</v>
+      </c>
+      <c r="I107" s="5" t="n">
+        <v>928760.22</v>
+      </c>
+      <c r="J107" s="5" t="n">
+        <v>12909.77</v>
+      </c>
+      <c r="K107" s="6" t="n">
+        <v>10085.83</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>958360.22</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Nasdaq_100_E_mini</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" t="n">
+        <v>1.533</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>1.533</v>
+      </c>
+      <c r="I108" s="5" t="n">
+        <v>915850.45</v>
+      </c>
+      <c r="J108" s="5" t="n">
+        <v>12730.32</v>
+      </c>
+      <c r="K108" s="6" t="n">
+        <v>19514.18</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>948274.4</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="I109" s="5" t="n">
+        <v>903120.13</v>
+      </c>
+      <c r="J109" s="5" t="n">
+        <v>12553.37</v>
+      </c>
+      <c r="K109" s="6" t="n">
+        <v>6236.22</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>964596.45</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="I110" s="5" t="n">
+        <v>964596.45</v>
+      </c>
+      <c r="J110" s="5" t="n">
+        <v>13407.89</v>
+      </c>
+      <c r="K110" s="6" t="n">
+        <v>1260.09</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>965856.54</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" t="n">
+        <v>1.116</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="H111" t="n">
+        <v>1.109</v>
+      </c>
+      <c r="I111" s="5" t="n">
+        <v>951188.5600000001</v>
+      </c>
+      <c r="J111" s="5" t="n">
+        <v>13221.52</v>
+      </c>
+      <c r="K111" s="6" t="n">
+        <v>14664.75</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>980521.29</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/quickfixclose0_portfolio_daily.xlsx
+++ b/output/quickfixclose0_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$190</f>
+              <f>'equity_curve'!$A$2:$A$191</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$190</f>
+              <f>'equity_curve'!$B$2:$B$191</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>524,424.45</t>
+          <t>547,434.53</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+424.42%</t>
+          <t>+447.43%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>541,057  (+441.06%)</t>
+          <t>564,908  (+464.91%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8,266  (16.6 pts of return)</t>
+          <t>8,374  (17.5 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7645.8x</t>
+          <t>8060.3x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12">
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+1.59R  (best +9.14R)</t>
+          <t>+1.58R  (best +9.14R)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3,969  (+1.59%)</t>
+          <t>4,070  (+1.58%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-06</t>
+          <t>2025-12-18 -&gt; 2026-08-07</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5318,6 +5318,34 @@
         </is>
       </c>
     </row>
+    <row r="191">
+      <c r="A191" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B191" s="5" t="n">
+        <v>547434.53</v>
+      </c>
+      <c r="C191" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D191" s="5" t="n">
+        <v>547434.53</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures short (risk 5,244); NY_Palladium_Futures short (risk 5,192); NY_Platinum_Futures short (risk 5,140)</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures exit_close (+19,474); NY_Palladium_Futures exit_close (+1,649); NY_Platinum_Futures exit_close (+1,886)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5330,7 +5358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M111"/>
+  <dimension ref="A1:M114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -11025,6 +11053,159 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" t="n">
+        <v>3.719</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H112" t="n">
+        <v>3.713</v>
+      </c>
+      <c r="I112" s="5" t="n">
+        <v>980521.29</v>
+      </c>
+      <c r="J112" s="5" t="n">
+        <v>13629.25</v>
+      </c>
+      <c r="K112" s="6" t="n">
+        <v>50612.13</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>1031133.42</v>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>NY_Palladium_Futures</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="I113" s="5" t="n">
+        <v>966892.04</v>
+      </c>
+      <c r="J113" s="5" t="n">
+        <v>13439.8</v>
+      </c>
+      <c r="K113" s="6" t="n">
+        <v>4269.24</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>1035402.66</v>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>953452.24</v>
+      </c>
+      <c r="J114" s="5" t="n">
+        <v>13252.99</v>
+      </c>
+      <c r="K114" s="6" t="n">
+        <v>4863.97</v>
+      </c>
+      <c r="L114" s="5" t="n">
+        <v>1040266.63</v>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>exit_close</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
